--- a/output/pdf_financials_xlsx/TR.xlsx
+++ b/output/pdf_financials_xlsx/TR.xlsx
@@ -3984,25 +3984,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.01943</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.226703</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.226703</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.320605</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.34064</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.34064</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.9402199999999999</v>
       </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
@@ -6450,7 +6450,11 @@
           <t>Reserves (Note 8c)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -6910,7 +6914,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.01943</v>
       </c>

--- a/output/pdf_financials_xlsx/TR.xlsx
+++ b/output/pdf_financials_xlsx/TR.xlsx
@@ -824,19 +824,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005171</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003127</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000561</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002634</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001515</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1422,19 +1422,19 @@
         <v>-0.077207</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.411294</v>
+        <v>-0.416465</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.494135</v>
+        <v>-0.497262</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.354054</v>
+        <v>-0.354615</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.252887</v>
+        <v>-0.255521</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.242446</v>
+        <v>-0.243961</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-2.096543</v>
@@ -1498,19 +1498,19 @@
         <v>-0.077207</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.411294</v>
+        <v>-0.416465</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.494135</v>
+        <v>-0.497262</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.354054</v>
+        <v>-0.354615</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.252887</v>
+        <v>-0.255521</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.242446</v>
+        <v>-0.243961</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-2.096543</v>
@@ -1682,19 +1682,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.736278</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.632073</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.070268</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.127227</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.085967</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.04892</v>
@@ -1758,19 +1758,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.736278</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.632073</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.070268</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.127227</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.085967</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.04892</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.739776</v>
+        <v>0.003498</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.72927</v>
+        <v>0.09719700000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07424699999999999</v>
+        <v>0.003979</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.127227</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.09117500000000001</v>
+        <v>0.005208</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.005208</v>
@@ -5151,10 +5151,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04551</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.129216</v>
       </c>
       <c r="J124" s="1" t="inlineStr">
         <is>
@@ -5187,10 +5187,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04551</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.129216</v>
       </c>
       <c r="J125" s="1" t="inlineStr">
         <is>
@@ -6080,7 +6080,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -6641,7 +6645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -6694,7 +6698,11 @@
           <t>Reclamation deposit (Note 4)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.0075</v>
       </c>
@@ -8182,7 +8190,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -14320,7 +14332,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -15109,7 +15121,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
